--- a/relatorios/relatorio_faturamento_2024-01-01_a_2024-12-31.xlsx
+++ b/relatorios/relatorio_faturamento_2024-01-01_a_2024-12-31.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -602,7 +602,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -611,16 +611,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -629,16 +629,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -647,16 +647,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -665,16 +665,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -683,16 +683,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -701,16 +701,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -719,16 +719,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -737,16 +737,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -755,16 +755,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>45352</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -773,16 +773,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>45352</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -791,16 +791,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>45352</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -809,16 +809,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>45352</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -827,16 +827,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>45352</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -845,16 +845,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>45352</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -863,16 +863,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>45352</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -881,9 +881,1629 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="D25" s="2" t="n">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Unidade A</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unidade A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unidade A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unidade A</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unidade A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unidade A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unidade A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unidade A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unidade A</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unidade A</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unidade A</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unidade A</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unidade A</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unidade A</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D115" s="2" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -955,7 +2575,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="C2" t="n">
         <v>1000</v>
@@ -986,7 +2606,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="C3" t="n">
         <v>1500</v>
@@ -1017,7 +2637,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="C4" t="n">
         <v>2000</v>

--- a/relatorios/relatorio_faturamento_2024-01-01_a_2024-12-31.xlsx
+++ b/relatorios/relatorio_faturamento_2024-01-01_a_2024-12-31.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D115"/>
+  <dimension ref="A1:D175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1142,7 +1142,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1151,16 +1151,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1169,16 +1169,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1187,16 +1187,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1205,16 +1205,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1223,16 +1223,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1241,16 +1241,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1259,16 +1259,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1277,16 +1277,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1295,16 +1295,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1313,16 +1313,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1331,16 +1331,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1349,16 +1349,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1367,16 +1367,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1385,16 +1385,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1403,16 +1403,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1421,16 +1421,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1439,16 +1439,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1457,16 +1457,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1475,16 +1475,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="60">
@@ -1826,7 +1826,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1835,16 +1835,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1853,16 +1853,16 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1871,16 +1871,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1889,16 +1889,16 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1907,16 +1907,16 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1925,16 +1925,16 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -1943,16 +1943,16 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -1961,16 +1961,16 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -1979,16 +1979,16 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2015,16 +2015,16 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2033,16 +2033,16 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2051,16 +2051,16 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2069,16 +2069,16 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2087,16 +2087,16 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2105,16 +2105,16 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2123,16 +2123,16 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2141,16 +2141,16 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2159,16 +2159,16 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2177,16 +2177,16 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2195,16 +2195,16 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2213,16 +2213,16 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2231,16 +2231,16 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2249,16 +2249,16 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2267,16 +2267,16 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2285,16 +2285,16 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2303,16 +2303,16 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2321,16 +2321,16 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2339,16 +2339,16 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2357,16 +2357,16 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2375,16 +2375,16 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2393,16 +2393,16 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2411,16 +2411,16 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2429,16 +2429,16 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2447,16 +2447,16 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2465,16 +2465,16 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2483,16 +2483,16 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2501,9 +2501,1089 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D115" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Unidade B</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D158" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D160" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D162" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D163" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D164" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D165" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D166" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D167" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D168" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D169" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D170" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D171" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D172" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D173" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D174" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D175" s="2" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -2575,7 +3655,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="C2" t="n">
         <v>1000</v>
@@ -2606,7 +3686,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="C3" t="n">
         <v>1500</v>
@@ -2637,7 +3717,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="C4" t="n">
         <v>2000</v>

--- a/relatorios/relatorio_faturamento_2024-01-01_a_2024-12-31.xlsx
+++ b/relatorios/relatorio_faturamento_2024-01-01_a_2024-12-31.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D175"/>
+  <dimension ref="A1:D199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1502,7 +1502,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1511,16 +1511,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1529,16 +1529,16 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1547,16 +1547,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1565,16 +1565,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1583,16 +1583,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1601,16 +1601,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D65" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="68">
@@ -2546,7 +2546,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2555,16 +2555,16 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2573,16 +2573,16 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2591,16 +2591,16 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2609,16 +2609,16 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2627,16 +2627,16 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D122" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2645,16 +2645,16 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -2663,16 +2663,16 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -2681,16 +2681,16 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2699,16 +2699,16 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2717,16 +2717,16 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2735,16 +2735,16 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2753,16 +2753,16 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -2771,16 +2771,16 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D130" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -2789,16 +2789,16 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -2807,16 +2807,16 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D132" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="134">
@@ -3584,6 +3584,438 @@
         <v>2000</v>
       </c>
       <c r="D175" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D176" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D177" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D178" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D179" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D180" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D181" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D182" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D183" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D184" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D185" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D186" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D187" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D188" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D189" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D190" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D191" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D192" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D193" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D194" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D195" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D196" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D197" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D198" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D199" s="2" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -3655,7 +4087,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C2" t="n">
         <v>1000</v>
@@ -3686,7 +4118,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C3" t="n">
         <v>1500</v>
@@ -3717,7 +4149,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C4" t="n">
         <v>2000</v>

--- a/relatorios/relatorio_faturamento_2024-01-01_a_2024-12-31.xlsx
+++ b/relatorios/relatorio_faturamento_2024-01-01_a_2024-12-31.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D199"/>
+  <dimension ref="A1:D211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1646,7 +1646,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1655,16 +1655,16 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1673,16 +1673,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1691,16 +1691,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Unidade B</t>
+          <t>Unidade A</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
     </row>
     <row r="72">
@@ -2834,7 +2834,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -2843,16 +2843,16 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -2861,16 +2861,16 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -2879,16 +2879,16 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -2897,16 +2897,16 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D137" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -2915,16 +2915,16 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -2933,16 +2933,16 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -2951,16 +2951,16 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D140" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Unidade C</t>
+          <t>Unidade B</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
     </row>
     <row r="142">
@@ -4016,6 +4016,222 @@
         <v>2000</v>
       </c>
       <c r="D199" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D200" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D201" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D202" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D203" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D204" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D205" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D206" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D207" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D208" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D209" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D210" s="2" t="n">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Unidade C</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Faturamento</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D211" s="2" t="n">
         <v>45352</v>
       </c>
     </row>
@@ -4087,7 +4303,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C2" t="n">
         <v>1000</v>
@@ -4118,7 +4334,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C3" t="n">
         <v>1500</v>
@@ -4149,7 +4365,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C4" t="n">
         <v>2000</v>
